--- a/config/ISBSG2016R1_1_financial_industry_seed.xlsx
+++ b/config/ISBSG2016R1_1_financial_industry_seed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdche\Documents\GitHub\early_agile_estimator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A795F410-3A82-440D-B156-27CD6B7B72CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3F3F3F-31CB-4139-ABAE-23D5C364CC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="1810" windowWidth="22590" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1470" windowWidth="22590" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11300" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11300" uniqueCount="266">
   <si>
     <t>ISBSG Project ID</t>
   </si>
@@ -801,9 +801,6 @@
     <t>PL/SQL</t>
   </si>
   <si>
-    <t>Finance;</t>
-  </si>
-  <si>
     <t>Accounting system;</t>
   </si>
   <si>
@@ -1159,6 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AY940"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1322,7 +1320,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>10029</v>
       </c>
@@ -1381,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10032</v>
       </c>
@@ -1461,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>10066</v>
       </c>
@@ -1526,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>10067</v>
       </c>
@@ -1579,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>10075</v>
       </c>
@@ -1668,7 +1666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10090</v>
       </c>
@@ -1727,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>10151</v>
       </c>
@@ -1810,7 +1808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>10159</v>
       </c>
@@ -1884,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>10176</v>
       </c>
@@ -1943,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10232</v>
       </c>
@@ -2005,7 +2003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10279</v>
       </c>
@@ -2085,7 +2083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10283</v>
       </c>
@@ -2189,7 +2187,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>10358</v>
       </c>
@@ -2272,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10390</v>
       </c>
@@ -2349,7 +2347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10430</v>
       </c>
@@ -2411,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>10434</v>
       </c>
@@ -2485,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>10442</v>
       </c>
@@ -2544,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>10500</v>
       </c>
@@ -2612,7 +2610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10505</v>
       </c>
@@ -2686,7 +2684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>10513</v>
       </c>
@@ -2760,7 +2758,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>10519</v>
       </c>
@@ -2819,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>10523</v>
       </c>
@@ -2878,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>10525</v>
       </c>
@@ -2958,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>10532</v>
       </c>
@@ -3017,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>10570</v>
       </c>
@@ -3109,7 +3107,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>10581</v>
       </c>
@@ -3192,7 +3190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>10587</v>
       </c>
@@ -3275,7 +3273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>10607</v>
       </c>
@@ -3334,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>10621</v>
       </c>
@@ -3408,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>10662</v>
       </c>
@@ -3467,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>10663</v>
       </c>
@@ -3541,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>10682</v>
       </c>
@@ -3600,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>10718</v>
       </c>
@@ -3653,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>10721</v>
       </c>
@@ -3733,7 +3731,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>10733</v>
       </c>
@@ -3810,7 +3808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>10756</v>
       </c>
@@ -3869,7 +3867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>10765</v>
       </c>
@@ -3928,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>10777</v>
       </c>
@@ -3987,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>10783</v>
       </c>
@@ -4073,7 +4071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>10816</v>
       </c>
@@ -4144,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>10877</v>
       </c>
@@ -4218,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>10898</v>
       </c>
@@ -4343,7 +4341,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>10908</v>
       </c>
@@ -4402,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>10920</v>
       </c>
@@ -4461,7 +4459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>10925</v>
       </c>
@@ -4520,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>10981</v>
       </c>
@@ -4600,7 +4598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>10997</v>
       </c>
@@ -4686,7 +4684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>11027</v>
       </c>
@@ -4745,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>11044</v>
       </c>
@@ -4816,7 +4814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>11120</v>
       </c>
@@ -4887,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>11148</v>
       </c>
@@ -4946,7 +4944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>11150</v>
       </c>
@@ -5014,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>11181</v>
       </c>
@@ -5076,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>11197</v>
       </c>
@@ -5153,7 +5151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>11200</v>
       </c>
@@ -5212,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>11213</v>
       </c>
@@ -5280,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>11225</v>
       </c>
@@ -5339,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>11310</v>
       </c>
@@ -5398,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>11376</v>
       </c>
@@ -5445,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>11399</v>
       </c>
@@ -5504,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>11425</v>
       </c>
@@ -5587,7 +5585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>11436</v>
       </c>
@@ -5664,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>11454</v>
       </c>
@@ -5780,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>11462</v>
       </c>
@@ -5854,7 +5852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>11468</v>
       </c>
@@ -5913,7 +5911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>11474</v>
       </c>
@@ -5996,7 +5994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>11476</v>
       </c>
@@ -6055,7 +6053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>11497</v>
       </c>
@@ -6135,7 +6133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>11538</v>
       </c>
@@ -6194,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>11555</v>
       </c>
@@ -6262,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>11558</v>
       </c>
@@ -6336,7 +6334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>11600</v>
       </c>
@@ -6407,7 +6405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>11651</v>
       </c>
@@ -6466,7 +6464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>11705</v>
       </c>
@@ -6531,7 +6529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>11714</v>
       </c>
@@ -6614,7 +6612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>11738</v>
       </c>
@@ -6694,7 +6692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>11760</v>
       </c>
@@ -6753,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>11782</v>
       </c>
@@ -6827,7 +6825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>11790</v>
       </c>
@@ -6904,7 +6902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>11791</v>
       </c>
@@ -6963,7 +6961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>11797</v>
       </c>
@@ -7034,7 +7032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>11812</v>
       </c>
@@ -7123,7 +7121,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>11828</v>
       </c>
@@ -7170,7 +7168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>11859</v>
       </c>
@@ -7244,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>11896</v>
       </c>
@@ -7312,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>11929</v>
       </c>
@@ -7377,7 +7375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>11947</v>
       </c>
@@ -7439,7 +7437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>11957</v>
       </c>
@@ -7504,7 +7502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>11968</v>
       </c>
@@ -7569,7 +7567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>11976</v>
       </c>
@@ -7640,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>11988</v>
       </c>
@@ -7702,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>12017</v>
       </c>
@@ -7788,7 +7786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>12034</v>
       </c>
@@ -7850,7 +7848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>12065</v>
       </c>
@@ -7912,7 +7910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>12069</v>
       </c>
@@ -8031,7 +8029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>12086</v>
       </c>
@@ -8141,7 +8139,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>12108</v>
       </c>
@@ -8203,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>12122</v>
       </c>
@@ -8277,7 +8275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>12133</v>
       </c>
@@ -8348,7 +8346,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>12167</v>
       </c>
@@ -8407,7 +8405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>12179</v>
       </c>
@@ -8481,7 +8479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>12180</v>
       </c>
@@ -8555,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>12235</v>
       </c>
@@ -8629,7 +8627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>12278</v>
       </c>
@@ -8709,7 +8707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>12313</v>
       </c>
@@ -8774,7 +8772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>12377</v>
       </c>
@@ -8848,7 +8846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>12425</v>
       </c>
@@ -8910,7 +8908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>12453</v>
       </c>
@@ -8984,7 +8982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>12515</v>
       </c>
@@ -9043,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>12529</v>
       </c>
@@ -9105,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>12600</v>
       </c>
@@ -9152,7 +9150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>12606</v>
       </c>
@@ -9226,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>12667</v>
       </c>
@@ -9303,7 +9301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>12674</v>
       </c>
@@ -9371,7 +9369,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="116" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>12720</v>
       </c>
@@ -9430,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>12725</v>
       </c>
@@ -9522,7 +9520,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="118" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>12749</v>
       </c>
@@ -9602,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>12763</v>
       </c>
@@ -9685,7 +9683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>12814</v>
       </c>
@@ -9744,7 +9742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>12821</v>
       </c>
@@ -9809,7 +9807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>12844</v>
       </c>
@@ -9874,7 +9872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>12877</v>
       </c>
@@ -9945,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>12898</v>
       </c>
@@ -10010,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>12916</v>
       </c>
@@ -10111,7 +10109,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="126" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>12923</v>
       </c>
@@ -10170,7 +10168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>12965</v>
       </c>
@@ -10229,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>12995</v>
       </c>
@@ -10291,7 +10289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>13009</v>
       </c>
@@ -10356,7 +10354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>13026</v>
       </c>
@@ -10436,7 +10434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>13047</v>
       </c>
@@ -10546,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>13052</v>
       </c>
@@ -10602,7 +10600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>13125</v>
       </c>
@@ -10667,7 +10665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>13133</v>
       </c>
@@ -10753,7 +10751,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>13163</v>
       </c>
@@ -10812,7 +10810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>13166</v>
       </c>
@@ -10880,7 +10878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>13189</v>
       </c>
@@ -10939,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>13190</v>
       </c>
@@ -11004,7 +11002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>13201</v>
       </c>
@@ -11051,7 +11049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>13248</v>
       </c>
@@ -11116,7 +11114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>13295</v>
       </c>
@@ -11163,7 +11161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>13304</v>
       </c>
@@ -11234,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>13347</v>
       </c>
@@ -11296,7 +11294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>13384</v>
       </c>
@@ -11376,7 +11374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>13397</v>
       </c>
@@ -11435,7 +11433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>13457</v>
       </c>
@@ -11494,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>13514</v>
       </c>
@@ -11556,7 +11554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>13518</v>
       </c>
@@ -11615,7 +11613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>13534</v>
       </c>
@@ -11674,7 +11672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>13544</v>
       </c>
@@ -11733,7 +11731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>13569</v>
       </c>
@@ -11789,7 +11787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>13626</v>
       </c>
@@ -11848,7 +11846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>13664</v>
       </c>
@@ -11922,7 +11920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>13667</v>
       </c>
@@ -11981,7 +11979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>13676</v>
       </c>
@@ -12055,7 +12053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>13680</v>
       </c>
@@ -12117,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>13695</v>
       </c>
@@ -12197,7 +12195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>13701</v>
       </c>
@@ -12256,7 +12254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>13711</v>
       </c>
@@ -12303,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>13755</v>
       </c>
@@ -12383,7 +12381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>13784</v>
       </c>
@@ -12463,7 +12461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>13789</v>
       </c>
@@ -12528,7 +12526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>13799</v>
       </c>
@@ -12653,7 +12651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>13803</v>
       </c>
@@ -12700,7 +12698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>13850</v>
       </c>
@@ -12747,7 +12745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>13858</v>
       </c>
@@ -12818,7 +12816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>13886</v>
       </c>
@@ -12877,7 +12875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>13900</v>
       </c>
@@ -12957,7 +12955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>13906</v>
       </c>
@@ -13031,7 +13029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>13911</v>
       </c>
@@ -13114,7 +13112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>13983</v>
       </c>
@@ -13173,7 +13171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>13994</v>
       </c>
@@ -13232,7 +13230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>13997</v>
       </c>
@@ -13306,7 +13304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>14030</v>
       </c>
@@ -13377,7 +13375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>14031</v>
       </c>
@@ -13451,7 +13449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>14052</v>
       </c>
@@ -13498,7 +13496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>14055</v>
       </c>
@@ -13563,7 +13561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>14058</v>
       </c>
@@ -13640,7 +13638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>14070</v>
       </c>
@@ -13699,7 +13697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>14167</v>
       </c>
@@ -13755,7 +13753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>14267</v>
       </c>
@@ -13814,7 +13812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>14294</v>
       </c>
@@ -13870,7 +13868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>14319</v>
       </c>
@@ -13941,7 +13939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>14350</v>
       </c>
@@ -14000,7 +13998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>14371</v>
       </c>
@@ -14065,7 +14063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>14372</v>
       </c>
@@ -14142,7 +14140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>14374</v>
       </c>
@@ -14216,7 +14214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>14387</v>
       </c>
@@ -14281,7 +14279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>14431</v>
       </c>
@@ -14340,7 +14338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>14438</v>
       </c>
@@ -14399,7 +14397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>14487</v>
       </c>
@@ -14491,7 +14489,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="192" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>14509</v>
       </c>
@@ -14553,7 +14551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>14513</v>
       </c>
@@ -14618,7 +14616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>14514</v>
       </c>
@@ -14695,7 +14693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>14588</v>
       </c>
@@ -14754,7 +14752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>14592</v>
       </c>
@@ -14813,7 +14811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>14630</v>
       </c>
@@ -14872,7 +14870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>14645</v>
       </c>
@@ -14946,7 +14944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>14696</v>
       </c>
@@ -15020,7 +15018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>14739</v>
       </c>
@@ -15094,7 +15092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>14764</v>
       </c>
@@ -15165,7 +15163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>14768</v>
       </c>
@@ -15230,7 +15228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>14784</v>
       </c>
@@ -15289,7 +15287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>14832</v>
       </c>
@@ -15387,7 +15385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>14837</v>
       </c>
@@ -15443,7 +15441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>14912</v>
       </c>
@@ -15523,7 +15521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>14919</v>
       </c>
@@ -15624,7 +15622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>14920</v>
       </c>
@@ -15683,7 +15681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>14945</v>
       </c>
@@ -15745,7 +15743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>14985</v>
       </c>
@@ -15861,7 +15859,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="211" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>14989</v>
       </c>
@@ -15914,7 +15912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>14991</v>
       </c>
@@ -15985,7 +15983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>15016</v>
       </c>
@@ -16047,7 +16045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>15038</v>
       </c>
@@ -16103,7 +16101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>15047</v>
       </c>
@@ -16165,7 +16163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>15049</v>
       </c>
@@ -16221,7 +16219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>15090</v>
       </c>
@@ -16292,7 +16290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>15092</v>
       </c>
@@ -16354,7 +16352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>15191</v>
       </c>
@@ -16416,7 +16414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>15223</v>
       </c>
@@ -16490,7 +16488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>15231</v>
       </c>
@@ -16570,7 +16568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>15240</v>
       </c>
@@ -16644,7 +16642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>15267</v>
       </c>
@@ -16703,7 +16701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>15288</v>
       </c>
@@ -16777,7 +16775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>15309</v>
       </c>
@@ -16842,7 +16840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>15314</v>
       </c>
@@ -16901,7 +16899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>15329</v>
       </c>
@@ -16975,7 +16973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>15354</v>
       </c>
@@ -17040,7 +17038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>15364</v>
       </c>
@@ -17105,7 +17103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>15398</v>
       </c>
@@ -17164,7 +17162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>15416</v>
       </c>
@@ -17241,7 +17239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>15422</v>
       </c>
@@ -17318,7 +17316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>15424</v>
       </c>
@@ -17380,7 +17378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>15443</v>
       </c>
@@ -17454,7 +17452,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="235" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>15449</v>
       </c>
@@ -17549,7 +17547,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="236" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>15464</v>
       </c>
@@ -17614,7 +17612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>15493</v>
       </c>
@@ -17670,7 +17668,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="238" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>15561</v>
       </c>
@@ -17732,7 +17730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>15589</v>
       </c>
@@ -17800,7 +17798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>15598</v>
       </c>
@@ -17874,7 +17872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>15610</v>
       </c>
@@ -17939,7 +17937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>15658</v>
       </c>
@@ -18013,7 +18011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>15694</v>
       </c>
@@ -18072,7 +18070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>15711</v>
       </c>
@@ -18131,7 +18129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>15723</v>
       </c>
@@ -18211,7 +18209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>15771</v>
       </c>
@@ -18273,7 +18271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>15798</v>
       </c>
@@ -18338,7 +18336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>15824</v>
       </c>
@@ -18397,7 +18395,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>15905</v>
       </c>
@@ -18456,7 +18454,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="250" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>15927</v>
       </c>
@@ -18515,7 +18513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>15944</v>
       </c>
@@ -18574,7 +18572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>15957</v>
       </c>
@@ -18636,7 +18634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>15973</v>
       </c>
@@ -18695,7 +18693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>15977</v>
       </c>
@@ -18760,7 +18758,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="255" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>15983</v>
       </c>
@@ -18819,7 +18817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>15986</v>
       </c>
@@ -18887,7 +18885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>15999</v>
       </c>
@@ -18934,7 +18932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>16016</v>
       </c>
@@ -18981,7 +18979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>16046</v>
       </c>
@@ -19028,7 +19026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>16081</v>
       </c>
@@ -19090,7 +19088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>16089</v>
       </c>
@@ -19170,7 +19168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>16115</v>
       </c>
@@ -19229,7 +19227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>16143</v>
       </c>
@@ -19288,7 +19286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>16162</v>
       </c>
@@ -19347,7 +19345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>16185</v>
       </c>
@@ -19409,7 +19407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>16211</v>
       </c>
@@ -19516,7 +19514,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="267" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>16217</v>
       </c>
@@ -19581,7 +19579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>16222</v>
       </c>
@@ -19652,7 +19650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>16313</v>
       </c>
@@ -19711,7 +19709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>16344</v>
       </c>
@@ -19770,7 +19768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>16350</v>
       </c>
@@ -19853,7 +19851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>16405</v>
       </c>
@@ -19933,7 +19931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>16437</v>
       </c>
@@ -20022,7 +20020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>16481</v>
       </c>
@@ -20096,7 +20094,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="275" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>16561</v>
       </c>
@@ -20170,7 +20168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>16563</v>
       </c>
@@ -20250,7 +20248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>16598</v>
       </c>
@@ -20333,7 +20331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>16646</v>
       </c>
@@ -20407,7 +20405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>16682</v>
       </c>
@@ -20532,7 +20530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>16685</v>
       </c>
@@ -20606,7 +20604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>16701</v>
       </c>
@@ -20674,7 +20672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>16725</v>
       </c>
@@ -20766,7 +20764,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="283" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>16779</v>
       </c>
@@ -20840,7 +20838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>16782</v>
       </c>
@@ -20905,7 +20903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>16844</v>
       </c>
@@ -20985,7 +20983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>16862</v>
       </c>
@@ -21053,7 +21051,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="287" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>16888</v>
       </c>
@@ -21112,7 +21110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>16897</v>
       </c>
@@ -21183,7 +21181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>16979</v>
       </c>
@@ -21242,7 +21240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>16985</v>
       </c>
@@ -21301,7 +21299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>17022</v>
       </c>
@@ -21372,7 +21370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>17047</v>
       </c>
@@ -21458,7 +21456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>17052</v>
       </c>
@@ -21532,7 +21530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>17061</v>
       </c>
@@ -21605,7 +21603,7 @@
         <v>71</v>
       </c>
       <c r="E295" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H295" t="s">
         <v>56</v>
@@ -21656,7 +21654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>17096</v>
       </c>
@@ -21715,7 +21713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>17127</v>
       </c>
@@ -21777,7 +21775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>17144</v>
       </c>
@@ -21833,7 +21831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>17173</v>
       </c>
@@ -21892,7 +21890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>17216</v>
       </c>
@@ -21957,7 +21955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>17261</v>
       </c>
@@ -22031,7 +22029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>17273</v>
       </c>
@@ -22111,7 +22109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>17280</v>
       </c>
@@ -22173,7 +22171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>17285</v>
       </c>
@@ -22295,7 +22293,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="305" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>17293</v>
       </c>
@@ -22375,7 +22373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>17309</v>
       </c>
@@ -22449,7 +22447,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="307" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>17331</v>
       </c>
@@ -22508,7 +22506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>17333</v>
       </c>
@@ -22579,7 +22577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>17372</v>
       </c>
@@ -22638,7 +22636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>17374</v>
       </c>
@@ -22712,7 +22710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>17438</v>
       </c>
@@ -22792,7 +22790,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="312" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>17460</v>
       </c>
@@ -22860,7 +22858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>17534</v>
       </c>
@@ -22928,7 +22926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>17546</v>
       </c>
@@ -22987,7 +22985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>17547</v>
       </c>
@@ -23043,7 +23041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>17558</v>
       </c>
@@ -23096,7 +23094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>17561</v>
       </c>
@@ -23167,7 +23165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>17563</v>
       </c>
@@ -23247,7 +23245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>17606</v>
       </c>
@@ -23369,7 +23367,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="320" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>17623</v>
       </c>
@@ -23431,7 +23429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>17648</v>
       </c>
@@ -23496,7 +23494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>17659</v>
       </c>
@@ -23561,7 +23559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>17661</v>
       </c>
@@ -23629,7 +23627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>17720</v>
       </c>
@@ -23712,7 +23710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>17723</v>
       </c>
@@ -23768,7 +23766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>17737</v>
       </c>
@@ -23833,7 +23831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>17743</v>
       </c>
@@ -23910,7 +23908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="328" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>17744</v>
       </c>
@@ -24005,7 +24003,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="329" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>17859</v>
       </c>
@@ -24064,7 +24062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>17874</v>
       </c>
@@ -24123,7 +24121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>17908</v>
       </c>
@@ -24188,7 +24186,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="332" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>17938</v>
       </c>
@@ -24247,7 +24245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>17954</v>
       </c>
@@ -24353,7 +24351,7 @@
         <v>71</v>
       </c>
       <c r="E334" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F334" t="s">
         <v>160</v>
@@ -24404,7 +24402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>17980</v>
       </c>
@@ -24469,7 +24467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>17984</v>
       </c>
@@ -24516,7 +24514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>17991</v>
       </c>
@@ -24599,7 +24597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>18004</v>
       </c>
@@ -24682,7 +24680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>18008</v>
       </c>
@@ -24741,7 +24739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>18019</v>
       </c>
@@ -24818,7 +24816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>18045</v>
       </c>
@@ -24877,7 +24875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>18051</v>
       </c>
@@ -24939,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>18083</v>
       </c>
@@ -25004,7 +25002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>18103</v>
       </c>
@@ -25060,7 +25058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>18118</v>
       </c>
@@ -25191,7 +25189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="346" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>18124</v>
       </c>
@@ -25238,7 +25236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>18144</v>
       </c>
@@ -25297,7 +25295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>18159</v>
       </c>
@@ -25356,7 +25354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>18182</v>
       </c>
@@ -25430,7 +25428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>18206</v>
       </c>
@@ -25501,7 +25499,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="351" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>18306</v>
       </c>
@@ -25563,7 +25561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>18328</v>
       </c>
@@ -25643,7 +25641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>18364</v>
       </c>
@@ -25717,7 +25715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>18385</v>
       </c>
@@ -25791,7 +25789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>18387</v>
       </c>
@@ -25876,7 +25874,7 @@
         <v>71</v>
       </c>
       <c r="E356" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F356" t="s">
         <v>160</v>
@@ -25933,7 +25931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>18398</v>
       </c>
@@ -26010,7 +26008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>18427</v>
       </c>
@@ -26090,7 +26088,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="359" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>18438</v>
       </c>
@@ -26164,7 +26162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>18442</v>
       </c>
@@ -26226,7 +26224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>18459</v>
       </c>
@@ -26297,7 +26295,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="362" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>18491</v>
       </c>
@@ -26359,7 +26357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>18493</v>
       </c>
@@ -26415,7 +26413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>18511</v>
       </c>
@@ -26474,7 +26472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>18513</v>
       </c>
@@ -26548,7 +26546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>18539</v>
       </c>
@@ -26607,7 +26605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>18551</v>
       </c>
@@ -26666,7 +26664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>18556</v>
       </c>
@@ -26728,7 +26726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>18577</v>
       </c>
@@ -26787,7 +26785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>18584</v>
       </c>
@@ -26846,7 +26844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>18607</v>
       </c>
@@ -26905,7 +26903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>18608</v>
       </c>
@@ -26952,7 +26950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>18609</v>
       </c>
@@ -27056,7 +27054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>18639</v>
       </c>
@@ -27118,7 +27116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>18650</v>
       </c>
@@ -27204,7 +27202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>18673</v>
       </c>
@@ -27287,7 +27285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>18703</v>
       </c>
@@ -27349,7 +27347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>18723</v>
       </c>
@@ -27420,7 +27418,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="379" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>18767</v>
       </c>
@@ -27479,7 +27477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>18770</v>
       </c>
@@ -27559,7 +27557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>18863</v>
       </c>
@@ -27639,7 +27637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>18873</v>
       </c>
@@ -27719,7 +27717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>18889</v>
       </c>
@@ -27766,7 +27764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>18903</v>
       </c>
@@ -27846,7 +27844,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="385" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>18945</v>
       </c>
@@ -27908,7 +27906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>18953</v>
       </c>
@@ -27967,7 +27965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>18988</v>
       </c>
@@ -28014,7 +28012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>19004</v>
       </c>
@@ -28073,7 +28071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>19052</v>
       </c>
@@ -28147,7 +28145,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="390" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>19088</v>
       </c>
@@ -28206,7 +28204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>19092</v>
       </c>
@@ -28274,7 +28272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>19135</v>
       </c>
@@ -28321,7 +28319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>19141</v>
       </c>
@@ -28431,7 +28429,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="394" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>19175</v>
       </c>
@@ -28487,7 +28485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>19209</v>
       </c>
@@ -28570,7 +28568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>19233</v>
       </c>
@@ -28650,7 +28648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>19249</v>
       </c>
@@ -28709,7 +28707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>19258</v>
       </c>
@@ -28771,7 +28769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>19271</v>
       </c>
@@ -28830,7 +28828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>19305</v>
       </c>
@@ -28904,7 +28902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>19339</v>
       </c>
@@ -28999,7 +28997,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="402" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>19343</v>
       </c>
@@ -29067,7 +29065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>19363</v>
       </c>
@@ -29147,7 +29145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>19364</v>
       </c>
@@ -29230,7 +29228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="405" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>19407</v>
       </c>
@@ -29289,7 +29287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>19410</v>
       </c>
@@ -29363,7 +29361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>19421</v>
       </c>
@@ -29437,7 +29435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>19427</v>
       </c>
@@ -29496,7 +29494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>19455</v>
       </c>
@@ -29564,7 +29562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>19464</v>
       </c>
@@ -29638,7 +29636,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="411" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>19472</v>
       </c>
@@ -29697,7 +29695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>19474</v>
       </c>
@@ -29756,7 +29754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>19542</v>
       </c>
@@ -29815,7 +29813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>19549</v>
       </c>
@@ -29862,7 +29860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>19557</v>
       </c>
@@ -29921,7 +29919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>19561</v>
       </c>
@@ -30040,7 +30038,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="417" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>19571</v>
       </c>
@@ -30099,7 +30097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>19618</v>
       </c>
@@ -30173,7 +30171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>19626</v>
       </c>
@@ -30235,7 +30233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>19627</v>
       </c>
@@ -30342,7 +30340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>19660</v>
       </c>
@@ -30404,7 +30402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>19685</v>
       </c>
@@ -30463,7 +30461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>19700</v>
       </c>
@@ -30525,7 +30523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>19764</v>
       </c>
@@ -30584,7 +30582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>19827</v>
       </c>
@@ -30637,7 +30635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>19829</v>
       </c>
@@ -30693,7 +30691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>19839</v>
       </c>
@@ -30767,7 +30765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>19872</v>
       </c>
@@ -30847,7 +30845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>19905</v>
       </c>
@@ -30921,7 +30919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>19912</v>
       </c>
@@ -30986,7 +30984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>19962</v>
       </c>
@@ -31045,7 +31043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>20117</v>
       </c>
@@ -31122,7 +31120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>20146</v>
       </c>
@@ -31169,7 +31167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>20194</v>
       </c>
@@ -31252,7 +31250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>20296</v>
       </c>
@@ -31299,7 +31297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>20361</v>
       </c>
@@ -31346,7 +31344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>20399</v>
       </c>
@@ -31405,7 +31403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>20430</v>
       </c>
@@ -31488,7 +31486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>20443</v>
       </c>
@@ -31571,7 +31569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>20457</v>
       </c>
@@ -31663,7 +31661,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="441" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>20504</v>
       </c>
@@ -31734,7 +31732,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="442" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>20506</v>
       </c>
@@ -31787,7 +31785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>20512</v>
       </c>
@@ -31879,7 +31877,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="444" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>20525</v>
       </c>
@@ -31965,7 +31963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>20540</v>
       </c>
@@ -32024,7 +32022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>20584</v>
       </c>
@@ -32071,7 +32069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>20628</v>
       </c>
@@ -32130,7 +32128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>20641</v>
       </c>
@@ -32219,7 +32217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="449" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>20680</v>
       </c>
@@ -32284,7 +32282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450">
         <v>20701</v>
       </c>
@@ -32367,7 +32365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451">
         <v>20724</v>
       </c>
@@ -32441,7 +32439,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="452" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452">
         <v>20732</v>
       </c>
@@ -32503,7 +32501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453">
         <v>20809</v>
       </c>
@@ -32574,7 +32572,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="454" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454">
         <v>20811</v>
       </c>
@@ -32666,7 +32664,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="455" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455">
         <v>20820</v>
       </c>
@@ -32731,7 +32729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456">
         <v>20882</v>
       </c>
@@ -32778,7 +32776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457">
         <v>20883</v>
       </c>
@@ -32858,7 +32856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>20896</v>
       </c>
@@ -32971,7 +32969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>20917</v>
       </c>
@@ -33018,7 +33016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>20926</v>
       </c>
@@ -33107,7 +33105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>20961</v>
       </c>
@@ -33154,7 +33152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>20964</v>
       </c>
@@ -33240,7 +33238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>20973</v>
       </c>
@@ -33314,7 +33312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>20979</v>
       </c>
@@ -33400,7 +33398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>20995</v>
       </c>
@@ -33468,7 +33466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>21068</v>
       </c>
@@ -33544,7 +33542,7 @@
         <v>71</v>
       </c>
       <c r="E467" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F467" t="s">
         <v>54</v>
@@ -33598,7 +33596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>21137</v>
       </c>
@@ -33681,7 +33679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="469" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>21140</v>
       </c>
@@ -33752,7 +33750,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="470" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>21150</v>
       </c>
@@ -33838,7 +33836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>21154</v>
       </c>
@@ -33942,7 +33940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>21174</v>
       </c>
@@ -34052,7 +34050,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="473" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>21263</v>
       </c>
@@ -34126,7 +34124,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="474" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>21271</v>
       </c>
@@ -34182,7 +34180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>21302</v>
       </c>
@@ -34256,7 +34254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>21311</v>
       </c>
@@ -34342,7 +34340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="477" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>21337</v>
       </c>
@@ -34404,7 +34402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>21383</v>
       </c>
@@ -34475,7 +34473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>21390</v>
       </c>
@@ -34549,7 +34547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>21424</v>
       </c>
@@ -34617,7 +34615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481">
         <v>21428</v>
       </c>
@@ -34691,7 +34689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482">
         <v>21436</v>
       </c>
@@ -34771,7 +34769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483">
         <v>21439</v>
       </c>
@@ -34830,7 +34828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484">
         <v>21443</v>
       </c>
@@ -34901,7 +34899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485">
         <v>21472</v>
       </c>
@@ -34969,7 +34967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486">
         <v>21487</v>
       </c>
@@ -35043,7 +35041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487">
         <v>21496</v>
       </c>
@@ -35117,7 +35115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488">
         <v>21529</v>
       </c>
@@ -35239,7 +35237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489">
         <v>21539</v>
       </c>
@@ -35307,7 +35305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490">
         <v>21569</v>
       </c>
@@ -35366,7 +35364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491">
         <v>21574</v>
       </c>
@@ -35440,7 +35438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492">
         <v>21575</v>
       </c>
@@ -35499,7 +35497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493">
         <v>21586</v>
       </c>
@@ -35564,7 +35562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494">
         <v>21589</v>
       </c>
@@ -35647,7 +35645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="495" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495">
         <v>21607</v>
       </c>
@@ -35706,7 +35704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496">
         <v>21665</v>
       </c>
@@ -35753,7 +35751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497">
         <v>21668</v>
       </c>
@@ -35833,7 +35831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498">
         <v>21686</v>
       </c>
@@ -35916,7 +35914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499">
         <v>21703</v>
       </c>
@@ -35975,7 +35973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500">
         <v>21711</v>
       </c>
@@ -36034,7 +36032,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="501" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501">
         <v>21729</v>
       </c>
@@ -36134,7 +36132,7 @@
         <v>71</v>
       </c>
       <c r="E502" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F502" t="s">
         <v>54</v>
@@ -36191,7 +36189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503">
         <v>21820</v>
       </c>
@@ -36262,7 +36260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504">
         <v>21854</v>
       </c>
@@ -36357,7 +36355,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="505" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505">
         <v>21873</v>
       </c>
@@ -36416,7 +36414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506">
         <v>21882</v>
       </c>
@@ -36463,7 +36461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507">
         <v>21925</v>
       </c>
@@ -36522,7 +36520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508">
         <v>21966</v>
       </c>
@@ -36581,7 +36579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="509" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509">
         <v>21975</v>
       </c>
@@ -36640,7 +36638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510">
         <v>22069</v>
       </c>
@@ -36720,7 +36718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511">
         <v>22097</v>
       </c>
@@ -36800,7 +36798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512">
         <v>22129</v>
       </c>
@@ -36895,7 +36893,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="513" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513">
         <v>22131</v>
       </c>
@@ -36960,7 +36958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514">
         <v>22135</v>
       </c>
@@ -37019,7 +37017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515">
         <v>22183</v>
       </c>
@@ -37078,7 +37076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516">
         <v>22185</v>
       </c>
@@ -37143,7 +37141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517">
         <v>22192</v>
       </c>
@@ -37208,7 +37206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518">
         <v>22238</v>
       </c>
@@ -37282,7 +37280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519">
         <v>22262</v>
       </c>
@@ -37347,7 +37345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520">
         <v>22265</v>
       </c>
@@ -37409,7 +37407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521">
         <v>22286</v>
       </c>
@@ -37468,7 +37466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522">
         <v>22296</v>
       </c>
@@ -37527,7 +37525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523">
         <v>22302</v>
       </c>
@@ -37649,7 +37647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524">
         <v>22308</v>
       </c>
@@ -37723,7 +37721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525">
         <v>22338</v>
       </c>
@@ -37812,7 +37810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="526" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526">
         <v>22370</v>
       </c>
@@ -37874,7 +37872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527">
         <v>22410</v>
       </c>
@@ -37933,7 +37931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528">
         <v>22427</v>
       </c>
@@ -37998,7 +37996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529">
         <v>22453</v>
       </c>
@@ -38060,7 +38058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530">
         <v>22507</v>
       </c>
@@ -38143,7 +38141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="531" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531">
         <v>22549</v>
       </c>
@@ -38202,7 +38200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532">
         <v>22579</v>
       </c>
@@ -38267,7 +38265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533">
         <v>22583</v>
       </c>
@@ -38326,7 +38324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534">
         <v>22604</v>
       </c>
@@ -38400,7 +38398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535">
         <v>22675</v>
       </c>
@@ -38447,7 +38445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536">
         <v>22699</v>
       </c>
@@ -38521,7 +38519,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="537" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537">
         <v>22712</v>
       </c>
@@ -38604,7 +38602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538">
         <v>22842</v>
       </c>
@@ -38711,7 +38709,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="539" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539">
         <v>22857</v>
       </c>
@@ -38791,7 +38789,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="540" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540">
         <v>22908</v>
       </c>
@@ -38853,7 +38851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541">
         <v>22958</v>
       </c>
@@ -38930,7 +38928,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="542" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542">
         <v>22991</v>
       </c>
@@ -39010,7 +39008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543">
         <v>23002</v>
       </c>
@@ -39066,7 +39064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544">
         <v>23009</v>
       </c>
@@ -39188,7 +39186,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="545" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545">
         <v>23063</v>
       </c>
@@ -39250,7 +39248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546">
         <v>23066</v>
       </c>
@@ -39321,7 +39319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547">
         <v>23091</v>
       </c>
@@ -39374,7 +39372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548">
         <v>23092</v>
       </c>
@@ -39442,7 +39440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549">
         <v>23093</v>
       </c>
@@ -39510,7 +39508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550">
         <v>23096</v>
       </c>
@@ -39569,7 +39567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551">
         <v>23120</v>
       </c>
@@ -39643,7 +39641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552">
         <v>23161</v>
       </c>
@@ -39714,7 +39712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553">
         <v>23173</v>
       </c>
@@ -39782,7 +39780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="554" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554">
         <v>23196</v>
       </c>
@@ -39841,7 +39839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555">
         <v>23232</v>
       </c>
@@ -39912,7 +39910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556">
         <v>23250</v>
       </c>
@@ -39971,7 +39969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557">
         <v>23341</v>
       </c>
@@ -40030,7 +40028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558">
         <v>23356</v>
       </c>
@@ -40113,7 +40111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559">
         <v>23385</v>
       </c>
@@ -40172,7 +40170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560">
         <v>23415</v>
       </c>
@@ -40234,7 +40232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561">
         <v>23425</v>
       </c>
@@ -40299,7 +40297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562">
         <v>23434</v>
       </c>
@@ -40358,7 +40356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563">
         <v>23437</v>
       </c>
@@ -40417,7 +40415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564">
         <v>23445</v>
       </c>
@@ -40482,7 +40480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565">
         <v>23459</v>
       </c>
@@ -40541,7 +40539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566">
         <v>23488</v>
       </c>
@@ -40600,7 +40598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567">
         <v>23489</v>
       </c>
@@ -40677,7 +40675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568">
         <v>23512</v>
       </c>
@@ -40736,7 +40734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569">
         <v>23561</v>
       </c>
@@ -40792,7 +40790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570">
         <v>23565</v>
       </c>
@@ -40848,7 +40846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571">
         <v>23587</v>
       </c>
@@ -40925,7 +40923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572">
         <v>23610</v>
       </c>
@@ -40984,7 +40982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573">
         <v>23643</v>
       </c>
@@ -41055,7 +41053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574">
         <v>23690</v>
       </c>
@@ -41138,7 +41136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575">
         <v>23768</v>
       </c>
@@ -41215,7 +41213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576">
         <v>23772</v>
       </c>
@@ -41277,7 +41275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577">
         <v>23861</v>
       </c>
@@ -41351,7 +41349,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="578" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578">
         <v>23884</v>
       </c>
@@ -41434,7 +41432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579">
         <v>23911</v>
       </c>
@@ -41493,7 +41491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580">
         <v>23918</v>
       </c>
@@ -41621,7 +41619,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="581" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581">
         <v>23920</v>
       </c>
@@ -41692,7 +41690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582">
         <v>23940</v>
       </c>
@@ -41763,7 +41761,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="583" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583">
         <v>23950</v>
       </c>
@@ -41822,7 +41820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584">
         <v>23980</v>
       </c>
@@ -41893,7 +41891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585">
         <v>23987</v>
       </c>
@@ -41940,7 +41938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586">
         <v>24023</v>
       </c>
@@ -42023,7 +42021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="587" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587">
         <v>24030</v>
       </c>
@@ -42103,7 +42101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588">
         <v>24042</v>
       </c>
@@ -42180,7 +42178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589">
         <v>24131</v>
       </c>
@@ -42254,7 +42252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590">
         <v>24193</v>
       </c>
@@ -42307,7 +42305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591">
         <v>24248</v>
       </c>
@@ -42375,7 +42373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592">
         <v>24302</v>
       </c>
@@ -42443,7 +42441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593">
         <v>24324</v>
       </c>
@@ -42502,7 +42500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594">
         <v>24333</v>
       </c>
@@ -42567,7 +42565,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="595" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595">
         <v>24335</v>
       </c>
@@ -42641,7 +42639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596">
         <v>24340</v>
       </c>
@@ -42688,7 +42686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597">
         <v>24350</v>
       </c>
@@ -42747,7 +42745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598">
         <v>24376</v>
       </c>
@@ -42824,7 +42822,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="599" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599">
         <v>24387</v>
       </c>
@@ -42901,7 +42899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="600" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600">
         <v>24420</v>
       </c>
@@ -42960,7 +42958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601">
         <v>24441</v>
       </c>
@@ -43046,7 +43044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="602" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602">
         <v>24481</v>
       </c>
@@ -43108,7 +43106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603">
         <v>24504</v>
       </c>
@@ -43179,7 +43177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="604" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604">
         <v>24528</v>
       </c>
@@ -43247,7 +43245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605">
         <v>24534</v>
       </c>
@@ -43306,7 +43304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606">
         <v>24568</v>
       </c>
@@ -43365,7 +43363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607">
         <v>24569</v>
       </c>
@@ -43448,7 +43446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608">
         <v>24574</v>
       </c>
@@ -43522,7 +43520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609">
         <v>24579</v>
       </c>
@@ -43596,7 +43594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610">
         <v>24585</v>
       </c>
@@ -43658,7 +43656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611">
         <v>24609</v>
       </c>
@@ -43714,7 +43712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612">
         <v>24627</v>
       </c>
@@ -43788,7 +43786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613">
         <v>24659</v>
       </c>
@@ -43862,7 +43860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614">
         <v>24768</v>
       </c>
@@ -43951,7 +43949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="615" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615">
         <v>24791</v>
       </c>
@@ -44013,7 +44011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616">
         <v>24797</v>
       </c>
@@ -44099,7 +44097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617">
         <v>24831</v>
       </c>
@@ -44161,7 +44159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618">
         <v>24930</v>
       </c>
@@ -44220,7 +44218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619">
         <v>24984</v>
       </c>
@@ -44279,7 +44277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620">
         <v>25123</v>
       </c>
@@ -44338,7 +44336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621">
         <v>25143</v>
       </c>
@@ -44397,7 +44395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622">
         <v>25145</v>
       </c>
@@ -44456,7 +44454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623">
         <v>25152</v>
       </c>
@@ -44515,7 +44513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624">
         <v>25195</v>
       </c>
@@ -44574,7 +44572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625">
         <v>25226</v>
       </c>
@@ -44633,7 +44631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626">
         <v>25231</v>
       </c>
@@ -44692,7 +44690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627">
         <v>25247</v>
       </c>
@@ -44772,7 +44770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628">
         <v>25278</v>
       </c>
@@ -44837,7 +44835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629">
         <v>25296</v>
       </c>
@@ -44896,7 +44894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630">
         <v>25332</v>
       </c>
@@ -44955,7 +44953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631">
         <v>25333</v>
       </c>
@@ -45014,7 +45012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632">
         <v>25336</v>
       </c>
@@ -45076,7 +45074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633">
         <v>25352</v>
       </c>
@@ -45138,7 +45136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634">
         <v>25403</v>
       </c>
@@ -45197,7 +45195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635">
         <v>25416</v>
       </c>
@@ -45256,7 +45254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636">
         <v>25427</v>
       </c>
@@ -45378,7 +45376,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="637" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637">
         <v>25443</v>
       </c>
@@ -45455,7 +45453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638">
         <v>25456</v>
       </c>
@@ -45538,7 +45536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639">
         <v>25484</v>
       </c>
@@ -45624,7 +45622,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="640" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640">
         <v>25486</v>
       </c>
@@ -45713,7 +45711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641">
         <v>25503</v>
       </c>
@@ -45772,7 +45770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642">
         <v>25528</v>
       </c>
@@ -45852,7 +45850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="643" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643">
         <v>25585</v>
       </c>
@@ -45914,7 +45912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644">
         <v>25599</v>
       </c>
@@ -46006,7 +46004,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="645" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645">
         <v>25694</v>
       </c>
@@ -46068,7 +46066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646">
         <v>25714</v>
       </c>
@@ -46148,7 +46146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647">
         <v>25715</v>
       </c>
@@ -46231,7 +46229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648">
         <v>25721</v>
       </c>
@@ -46290,7 +46288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649">
         <v>25725</v>
       </c>
@@ -46367,7 +46365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650">
         <v>25757</v>
       </c>
@@ -46447,7 +46445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651">
         <v>25788</v>
       </c>
@@ -46536,7 +46534,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="652" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652">
         <v>25790</v>
       </c>
@@ -46601,7 +46599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653">
         <v>25813</v>
       </c>
@@ -46660,7 +46658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654">
         <v>25821</v>
       </c>
@@ -46725,7 +46723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655">
         <v>25885</v>
       </c>
@@ -46799,7 +46797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656">
         <v>25898</v>
       </c>
@@ -46867,7 +46865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657">
         <v>25964</v>
       </c>
@@ -46935,7 +46933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658">
         <v>25965</v>
       </c>
@@ -47048,7 +47046,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="659" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659">
         <v>25986</v>
       </c>
@@ -47110,7 +47108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660">
         <v>26012</v>
       </c>
@@ -47175,7 +47173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661">
         <v>26013</v>
       </c>
@@ -47234,7 +47232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662">
         <v>26038</v>
       </c>
@@ -47308,7 +47306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663">
         <v>26103</v>
       </c>
@@ -47355,7 +47353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664">
         <v>26111</v>
       </c>
@@ -47429,7 +47427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665">
         <v>26168</v>
       </c>
@@ -47500,7 +47498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666">
         <v>26194</v>
       </c>
@@ -47559,7 +47557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667">
         <v>26196</v>
       </c>
@@ -47633,7 +47631,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="668" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668">
         <v>26230</v>
       </c>
@@ -47692,7 +47690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669">
         <v>26234</v>
       </c>
@@ -47787,7 +47785,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="670" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670">
         <v>26235</v>
       </c>
@@ -47846,7 +47844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671">
         <v>26247</v>
       </c>
@@ -47911,7 +47909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672">
         <v>26256</v>
       </c>
@@ -47970,7 +47968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673">
         <v>26292</v>
       </c>
@@ -48053,7 +48051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674">
         <v>26325</v>
       </c>
@@ -48112,7 +48110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675">
         <v>26331</v>
       </c>
@@ -48195,7 +48193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676">
         <v>26341</v>
       </c>
@@ -48290,7 +48288,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="677" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677">
         <v>26348</v>
       </c>
@@ -48349,7 +48347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678">
         <v>26363</v>
       </c>
@@ -48405,7 +48403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679">
         <v>26500</v>
       </c>
@@ -48491,7 +48489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="680" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680">
         <v>26531</v>
       </c>
@@ -48565,7 +48563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681">
         <v>26556</v>
       </c>
@@ -48618,7 +48616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682">
         <v>26579</v>
       </c>
@@ -48680,7 +48678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683">
         <v>26602</v>
       </c>
@@ -48739,7 +48737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684">
         <v>26628</v>
       </c>
@@ -48801,7 +48799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685">
         <v>26673</v>
       </c>
@@ -48863,7 +48861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686">
         <v>26694</v>
       </c>
@@ -48925,7 +48923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="687" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687">
         <v>26721</v>
       </c>
@@ -48987,7 +48985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688">
         <v>26758</v>
       </c>
@@ -49034,7 +49032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689">
         <v>26764</v>
       </c>
@@ -49099,7 +49097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690">
         <v>26770</v>
       </c>
@@ -49173,7 +49171,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="691" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691">
         <v>26775</v>
       </c>
@@ -49262,7 +49260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="692" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692">
         <v>26855</v>
       </c>
@@ -49330,7 +49328,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="693" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A693">
         <v>26865</v>
       </c>
@@ -49344,7 +49342,7 @@
         <v>71</v>
       </c>
       <c r="E693" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F693" t="s">
         <v>54</v>
@@ -49419,7 +49417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="694" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694">
         <v>26898</v>
       </c>
@@ -49481,7 +49479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695">
         <v>26911</v>
       </c>
@@ -49537,7 +49535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696">
         <v>26917</v>
       </c>
@@ -49596,7 +49594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697">
         <v>26921</v>
       </c>
@@ -49676,7 +49674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698">
         <v>26946</v>
       </c>
@@ -49735,7 +49733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699">
         <v>26984</v>
       </c>
@@ -49809,7 +49807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700">
         <v>26988</v>
       </c>
@@ -49880,7 +49878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701">
         <v>27022</v>
       </c>
@@ -49969,7 +49967,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="702" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702">
         <v>27058</v>
       </c>
@@ -50055,7 +50053,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="703" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703">
         <v>27060</v>
       </c>
@@ -50135,7 +50133,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="704" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704">
         <v>27063</v>
       </c>
@@ -50215,7 +50213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705">
         <v>27084</v>
       </c>
@@ -50277,7 +50275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706">
         <v>27105</v>
       </c>
@@ -50342,7 +50340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707">
         <v>27178</v>
       </c>
@@ -50449,7 +50447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="708" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708">
         <v>27237</v>
       </c>
@@ -50496,7 +50494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709">
         <v>27247</v>
       </c>
@@ -50570,7 +50568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710">
         <v>27260</v>
       </c>
@@ -50629,7 +50627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711">
         <v>27311</v>
       </c>
@@ -50700,7 +50698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712">
         <v>27318</v>
       </c>
@@ -50780,7 +50778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713">
         <v>27333</v>
       </c>
@@ -50860,7 +50858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714">
         <v>27348</v>
       </c>
@@ -50919,7 +50917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A715">
         <v>27392</v>
       </c>
@@ -50978,7 +50976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A716">
         <v>27441</v>
       </c>
@@ -51025,7 +51023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717">
         <v>27455</v>
       </c>
@@ -51099,7 +51097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A718">
         <v>27490</v>
       </c>
@@ -51173,7 +51171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A719">
         <v>27529</v>
       </c>
@@ -51259,7 +51257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="720" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:48" hidden="1" x14ac:dyDescent="0.35">
       <c r="A720">
         <v>27537</v>
       </c>
@@ -51321,7 +51319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A721">
         <v>27547</v>
       </c>
@@ -51386,7 +51384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A722">
         <v>27570</v>
       </c>
@@ -51445,7 +51443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A723">
         <v>27636</v>
       </c>
@@ -51504,7 +51502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724">
         <v>27649</v>
       </c>
@@ -51563,7 +51561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725">
         <v>27668</v>
       </c>
@@ -51616,7 +51614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A726">
         <v>27674</v>
       </c>
@@ -51708,7 +51706,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="727" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A727">
         <v>27703</v>
       </c>
@@ -51755,7 +51753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A728">
         <v>27705</v>
       </c>
@@ -51829,7 +51827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A729">
         <v>27716</v>
       </c>
@@ -51876,7 +51874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A730">
         <v>27752</v>
       </c>
@@ -51935,7 +51933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A731">
         <v>27765</v>
       </c>
@@ -52057,7 +52055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A732">
         <v>27770</v>
       </c>
@@ -52116,7 +52114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="733" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733">
         <v>27806</v>
       </c>
@@ -52217,7 +52215,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="734" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A734">
         <v>27862</v>
       </c>
@@ -52294,7 +52292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="735" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A735">
         <v>27865</v>
       </c>
@@ -52341,7 +52339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A736">
         <v>27897</v>
       </c>
@@ -52424,7 +52422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="737" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A737">
         <v>27909</v>
       </c>
@@ -52486,7 +52484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738">
         <v>27917</v>
       </c>
@@ -52545,7 +52543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739">
         <v>27938</v>
       </c>
@@ -52619,7 +52617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="740" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740">
         <v>27958</v>
       </c>
@@ -52687,7 +52685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741">
         <v>27970</v>
       </c>
@@ -52767,7 +52765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="742" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742">
         <v>27981</v>
       </c>
@@ -52853,7 +52851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A743">
         <v>27989</v>
       </c>
@@ -52915,7 +52913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A744">
         <v>27996</v>
       </c>
@@ -52989,7 +52987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A745">
         <v>28015</v>
       </c>
@@ -53063,7 +53061,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="746" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A746">
         <v>28037</v>
       </c>
@@ -53146,7 +53144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A747">
         <v>28043</v>
       </c>
@@ -53208,7 +53206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A748">
         <v>28046</v>
       </c>
@@ -53282,7 +53280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="749" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A749">
         <v>28080</v>
       </c>
@@ -53350,7 +53348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A750">
         <v>28159</v>
       </c>
@@ -53415,7 +53413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="751" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A751">
         <v>28170</v>
       </c>
@@ -53462,7 +53460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A752">
         <v>28180</v>
       </c>
@@ -53548,7 +53546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="753" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A753">
         <v>28199</v>
       </c>
@@ -53607,7 +53605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A754">
         <v>28203</v>
       </c>
@@ -53687,7 +53685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A755">
         <v>28206</v>
       </c>
@@ -53755,7 +53753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A756">
         <v>28283</v>
       </c>
@@ -53829,7 +53827,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="757" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A757">
         <v>28291</v>
       </c>
@@ -53891,7 +53889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A758">
         <v>28312</v>
       </c>
@@ -53950,7 +53948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A759">
         <v>28321</v>
       </c>
@@ -54024,7 +54022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A760">
         <v>28322</v>
       </c>
@@ -54113,7 +54111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="761" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A761">
         <v>28332</v>
       </c>
@@ -54172,7 +54170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A762">
         <v>28368</v>
       </c>
@@ -54231,7 +54229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A763">
         <v>28393</v>
       </c>
@@ -54311,7 +54309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A764">
         <v>28401</v>
       </c>
@@ -54394,7 +54392,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="765" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A765">
         <v>28416</v>
       </c>
@@ -54453,7 +54451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A766">
         <v>28431</v>
       </c>
@@ -54536,7 +54534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="767" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A767">
         <v>28550</v>
       </c>
@@ -54625,7 +54623,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="768" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A768">
         <v>28556</v>
       </c>
@@ -54684,7 +54682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A769">
         <v>28558</v>
       </c>
@@ -54743,7 +54741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A770">
         <v>28589</v>
       </c>
@@ -54859,7 +54857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A771">
         <v>28604</v>
       </c>
@@ -54915,7 +54913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="772" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A772">
         <v>28650</v>
       </c>
@@ -54986,7 +54984,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="773" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A773">
         <v>28652</v>
       </c>
@@ -55045,7 +55043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A774">
         <v>28667</v>
       </c>
@@ -55137,7 +55135,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="775" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A775">
         <v>28686</v>
       </c>
@@ -55255,7 +55253,7 @@
         <v>71</v>
       </c>
       <c r="E776" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F776" t="s">
         <v>54</v>
@@ -55312,7 +55310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="777" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777">
         <v>28760</v>
       </c>
@@ -55386,7 +55384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A778">
         <v>28777</v>
       </c>
@@ -55460,7 +55458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A779">
         <v>28826</v>
       </c>
@@ -55525,7 +55523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="780" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A780">
         <v>28831</v>
       </c>
@@ -55584,7 +55582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A781">
         <v>28851</v>
       </c>
@@ -55658,7 +55656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A782">
         <v>28858</v>
       </c>
@@ -55723,7 +55721,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="783" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A783">
         <v>28889</v>
       </c>
@@ -55782,7 +55780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A784">
         <v>28947</v>
       </c>
@@ -55841,7 +55839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="785" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A785">
         <v>28950</v>
       </c>
@@ -55900,7 +55898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A786">
         <v>28967</v>
       </c>
@@ -55992,7 +55990,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="787" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A787">
         <v>29221</v>
       </c>
@@ -56072,7 +56070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="788" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A788">
         <v>29248</v>
       </c>
@@ -56131,7 +56129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A789">
         <v>29265</v>
       </c>
@@ -56190,7 +56188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A790">
         <v>29268</v>
       </c>
@@ -56243,7 +56241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A791">
         <v>29308</v>
       </c>
@@ -56332,7 +56330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="792" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A792">
         <v>29382</v>
       </c>
@@ -56406,7 +56404,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="793" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A793">
         <v>29415</v>
       </c>
@@ -56480,7 +56478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="794" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A794">
         <v>29491</v>
       </c>
@@ -56569,7 +56567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="795" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A795">
         <v>29499</v>
       </c>
@@ -56616,7 +56614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A796">
         <v>29502</v>
       </c>
@@ -56675,7 +56673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A797">
         <v>29552</v>
       </c>
@@ -56734,7 +56732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A798">
         <v>29557</v>
       </c>
@@ -56796,7 +56794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A799">
         <v>29564</v>
       </c>
@@ -56855,7 +56853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A800">
         <v>29569</v>
       </c>
@@ -56938,7 +56936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A801">
         <v>29581</v>
       </c>
@@ -57012,7 +57010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="802" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A802">
         <v>29644</v>
       </c>
@@ -57134,7 +57132,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="803" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A803">
         <v>29647</v>
       </c>
@@ -57226,7 +57224,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="804" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A804">
         <v>29653</v>
       </c>
@@ -57285,7 +57283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A805">
         <v>29660</v>
       </c>
@@ -57344,7 +57342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A806">
         <v>29691</v>
       </c>
@@ -57391,7 +57389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A807">
         <v>29726</v>
       </c>
@@ -57471,7 +57469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="808" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A808">
         <v>29737</v>
       </c>
@@ -57539,7 +57537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A809">
         <v>29742</v>
       </c>
@@ -57616,7 +57614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="810" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A810">
         <v>29790</v>
       </c>
@@ -57681,7 +57679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A811">
         <v>29816</v>
       </c>
@@ -57755,7 +57753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="812" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A812">
         <v>29817</v>
       </c>
@@ -57814,7 +57812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="813" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A813">
         <v>29863</v>
       </c>
@@ -57870,7 +57868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A814">
         <v>29870</v>
       </c>
@@ -57929,7 +57927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A815">
         <v>29893</v>
       </c>
@@ -57997,7 +57995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A816">
         <v>29903</v>
       </c>
@@ -58071,7 +58069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A817">
         <v>29945</v>
       </c>
@@ -58172,7 +58170,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="818" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A818">
         <v>29959</v>
       </c>
@@ -58237,7 +58235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A819">
         <v>29997</v>
       </c>
@@ -58284,7 +58282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="820" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A820">
         <v>29999</v>
       </c>
@@ -58343,7 +58341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A821">
         <v>30029</v>
       </c>
@@ -58423,7 +58421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="822" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A822">
         <v>30317</v>
       </c>
@@ -58482,7 +58480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A823">
         <v>30345</v>
       </c>
@@ -58547,7 +58545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A824">
         <v>30355</v>
       </c>
@@ -58624,7 +58622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A825">
         <v>30358</v>
       </c>
@@ -58683,7 +58681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="826" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A826">
         <v>30426</v>
       </c>
@@ -58793,7 +58791,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="827" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A827">
         <v>30449</v>
       </c>
@@ -58855,7 +58853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="828" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A828">
         <v>30455</v>
       </c>
@@ -58983,7 +58981,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="829" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A829">
         <v>30484</v>
       </c>
@@ -59048,7 +59046,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="830" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A830">
         <v>30563</v>
       </c>
@@ -59122,7 +59120,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="831" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A831">
         <v>30567</v>
       </c>
@@ -59181,7 +59179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A832">
         <v>30585</v>
       </c>
@@ -59240,7 +59238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A833">
         <v>30595</v>
       </c>
@@ -59326,7 +59324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A834">
         <v>30606</v>
       </c>
@@ -59385,7 +59383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A835">
         <v>30609</v>
       </c>
@@ -59459,7 +59457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="836" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A836">
         <v>30611</v>
       </c>
@@ -59521,7 +59519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A837">
         <v>30621</v>
       </c>
@@ -59601,7 +59599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="838" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A838">
         <v>30627</v>
       </c>
@@ -59648,7 +59646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A839">
         <v>30636</v>
       </c>
@@ -59713,7 +59711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A840">
         <v>30640</v>
       </c>
@@ -59775,7 +59773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A841">
         <v>30642</v>
       </c>
@@ -59840,7 +59838,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="842" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A842">
         <v>30655</v>
       </c>
@@ -59887,7 +59885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A843">
         <v>30699</v>
       </c>
@@ -59958,7 +59956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="844" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A844">
         <v>30719</v>
       </c>
@@ -60017,7 +60015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A845">
         <v>30740</v>
       </c>
@@ -60079,7 +60077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A846">
         <v>30743</v>
       </c>
@@ -60195,7 +60193,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="847" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A847">
         <v>30773</v>
       </c>
@@ -60266,7 +60264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A848">
         <v>30788</v>
       </c>
@@ -60343,7 +60341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A849">
         <v>30803</v>
       </c>
@@ -60450,7 +60448,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="850" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A850">
         <v>30815</v>
       </c>
@@ -60524,7 +60522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A851">
         <v>30816</v>
       </c>
@@ -60583,7 +60581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A852">
         <v>30830</v>
       </c>
@@ -60630,7 +60628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A853">
         <v>30834</v>
       </c>
@@ -60704,7 +60702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="854" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A854">
         <v>30840</v>
       </c>
@@ -60766,7 +60764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A855">
         <v>30879</v>
       </c>
@@ -60828,7 +60826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="856" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A856">
         <v>30928</v>
       </c>
@@ -60902,7 +60900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A857">
         <v>30932</v>
       </c>
@@ -60961,7 +60959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="858" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A858">
         <v>30950</v>
       </c>
@@ -61023,7 +61021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A859">
         <v>30963</v>
       </c>
@@ -61097,7 +61095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A860">
         <v>30982</v>
       </c>
@@ -61159,7 +61157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A861">
         <v>30995</v>
       </c>
@@ -61233,7 +61231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A862">
         <v>31011</v>
       </c>
@@ -61358,7 +61356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="863" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A863">
         <v>31039</v>
       </c>
@@ -61429,7 +61427,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="864" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A864">
         <v>31043</v>
       </c>
@@ -61503,7 +61501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A865">
         <v>31076</v>
       </c>
@@ -61565,7 +61563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A866">
         <v>31103</v>
       </c>
@@ -61645,7 +61643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="867" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A867">
         <v>31123</v>
       </c>
@@ -61719,7 +61717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A868">
         <v>31127</v>
       </c>
@@ -61775,7 +61773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A869">
         <v>31164</v>
       </c>
@@ -61834,7 +61832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A870">
         <v>31169</v>
       </c>
@@ -61896,7 +61894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="871" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A871">
         <v>31240</v>
       </c>
@@ -61958,7 +61956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="872" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A872">
         <v>31286</v>
       </c>
@@ -62050,7 +62048,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="873" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A873">
         <v>31316</v>
       </c>
@@ -62133,7 +62131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="874" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A874">
         <v>31320</v>
       </c>
@@ -62213,7 +62211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="875" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A875">
         <v>31326</v>
       </c>
@@ -62308,7 +62306,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="876" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A876">
         <v>31331</v>
       </c>
@@ -62367,7 +62365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A877">
         <v>31333</v>
       </c>
@@ -62426,7 +62424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A878">
         <v>31394</v>
       </c>
@@ -62491,7 +62489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A879">
         <v>31447</v>
       </c>
@@ -62592,7 +62590,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="880" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A880">
         <v>31451</v>
       </c>
@@ -62654,7 +62652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A881">
         <v>31503</v>
       </c>
@@ -62728,7 +62726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="882" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A882">
         <v>31512</v>
       </c>
@@ -62793,7 +62791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A883">
         <v>31540</v>
       </c>
@@ -62867,7 +62865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A884">
         <v>31547</v>
       </c>
@@ -62926,7 +62924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="885" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A885">
         <v>31560</v>
       </c>
@@ -63048,7 +63046,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="886" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A886">
         <v>31585</v>
       </c>
@@ -63107,7 +63105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A887">
         <v>31627</v>
       </c>
@@ -63190,7 +63188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="888" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A888">
         <v>31631</v>
       </c>
@@ -63243,7 +63241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A889">
         <v>31636</v>
       </c>
@@ -63302,7 +63300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A890">
         <v>31680</v>
       </c>
@@ -63412,7 +63410,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="891" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A891">
         <v>31737</v>
       </c>
@@ -63486,7 +63484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="892" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A892">
         <v>31816</v>
       </c>
@@ -63581,7 +63579,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="893" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A893">
         <v>31817</v>
       </c>
@@ -63673,7 +63671,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="894" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A894">
         <v>31830</v>
       </c>
@@ -63732,7 +63730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:50" hidden="1" x14ac:dyDescent="0.35">
       <c r="A895">
         <v>31836</v>
       </c>
@@ -63805,13 +63803,13 @@
         <v>71</v>
       </c>
       <c r="E896" t="s">
+        <v>71</v>
+      </c>
+      <c r="F896" t="s">
+        <v>54</v>
+      </c>
+      <c r="G896" t="s">
         <v>257</v>
-      </c>
-      <c r="F896" t="s">
-        <v>54</v>
-      </c>
-      <c r="G896" t="s">
-        <v>258</v>
       </c>
       <c r="H896" t="s">
         <v>56</v>
@@ -63850,10 +63848,10 @@
         <v>67</v>
       </c>
       <c r="AC896" t="s">
+        <v>258</v>
+      </c>
+      <c r="AD896" t="s">
         <v>259</v>
-      </c>
-      <c r="AD896" t="s">
-        <v>260</v>
       </c>
       <c r="AG896" t="s">
         <v>96</v>
@@ -63889,10 +63887,10 @@
         <v>1745</v>
       </c>
       <c r="AX896" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="897" spans="1:51" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="897" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A897">
         <v>31969</v>
       </c>
@@ -63972,7 +63970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="898" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A898">
         <v>31972</v>
       </c>
@@ -64031,7 +64029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="899" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A899">
         <v>31978</v>
       </c>
@@ -64120,7 +64118,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="900" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A900">
         <v>31993</v>
       </c>
@@ -64179,7 +64177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A901">
         <v>32054</v>
       </c>
@@ -64253,7 +64251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="902" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A902">
         <v>32060</v>
       </c>
@@ -64312,7 +64310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="903" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A903">
         <v>32081</v>
       </c>
@@ -64374,7 +64372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="904" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A904">
         <v>32095</v>
       </c>
@@ -64442,7 +64440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="905" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A905">
         <v>32099</v>
       </c>
@@ -64507,7 +64505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="906" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A906">
         <v>32107</v>
       </c>
@@ -64581,7 +64579,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="907" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A907">
         <v>32113</v>
       </c>
@@ -64658,7 +64656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="908" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A908">
         <v>32130</v>
       </c>
@@ -64717,7 +64715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A909">
         <v>32148</v>
       </c>
@@ -64782,7 +64780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A910">
         <v>32161</v>
       </c>
@@ -64841,7 +64839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="911" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A911">
         <v>32170</v>
       </c>
@@ -64903,7 +64901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A912">
         <v>32207</v>
       </c>
@@ -64962,7 +64960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="913" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A913">
         <v>32227</v>
       </c>
@@ -65036,7 +65034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="914" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A914">
         <v>32236</v>
       </c>
@@ -65110,7 +65108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="915" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A915">
         <v>32243</v>
       </c>
@@ -65187,7 +65185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="916" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A916">
         <v>32255</v>
       </c>
@@ -65246,7 +65244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A917">
         <v>32275</v>
       </c>
@@ -65320,7 +65318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="918" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A918">
         <v>32291</v>
       </c>
@@ -65397,7 +65395,7 @@
         <v>67</v>
       </c>
       <c r="AC918" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD918" t="s">
         <v>201</v>
@@ -65445,7 +65443,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="919" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A919">
         <v>32318</v>
       </c>
@@ -65531,7 +65529,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="920" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A920">
         <v>32369</v>
       </c>
@@ -65587,7 +65585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A921">
         <v>32379</v>
       </c>
@@ -65649,7 +65647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="922" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A922">
         <v>32397</v>
       </c>
@@ -65729,7 +65727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A923">
         <v>32415</v>
       </c>
@@ -65788,7 +65786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A924">
         <v>32461</v>
       </c>
@@ -65874,7 +65872,7 @@
         <v>254</v>
       </c>
       <c r="AD924" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH924" t="s">
         <v>67</v>
@@ -65907,7 +65905,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="925" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A925">
         <v>32472</v>
       </c>
@@ -65966,7 +65964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A926">
         <v>32486</v>
       </c>
@@ -66052,7 +66050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="927" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A927">
         <v>32502</v>
       </c>
@@ -66123,7 +66121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="928" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A928">
         <v>32529</v>
       </c>
@@ -66188,7 +66186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="929" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A929">
         <v>32564</v>
       </c>
@@ -66283,7 +66281,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="930" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A930">
         <v>32589</v>
       </c>
@@ -66342,7 +66340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A931">
         <v>32590</v>
       </c>
@@ -66401,7 +66399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A932">
         <v>32599</v>
       </c>
@@ -66448,7 +66446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A933">
         <v>32604</v>
       </c>
@@ -66528,7 +66526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="934" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A934">
         <v>32627</v>
       </c>
@@ -66602,7 +66600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A935">
         <v>32659</v>
       </c>
@@ -66676,7 +66674,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="936" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A936">
         <v>32674</v>
       </c>
@@ -66735,7 +66733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="937" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A937">
         <v>32708</v>
       </c>
@@ -66812,7 +66810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="938" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A938">
         <v>32714</v>
       </c>
@@ -66844,7 +66842,7 @@
         <v>63</v>
       </c>
       <c r="K938" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L938">
         <v>156</v>
@@ -66877,7 +66875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A939">
         <v>32725</v>
       </c>
@@ -66957,7 +66955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="940" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:51" hidden="1" x14ac:dyDescent="0.35">
       <c r="A940">
         <v>32755</v>
       </c>
@@ -67011,7 +67009,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY940" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AY940" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Finance;"/>
+        <filter val="Financial; Banking, Insurance, Stock;"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>